--- a/PI-Manager-System/docs/订单管理总表.xlsx
+++ b/PI-Manager-System/docs/订单管理总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12525"/>
+    <workbookView windowWidth="28800" windowHeight="12075"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>订单日期</t>
   </si>
@@ -50,7 +50,10 @@
     <t>图片</t>
   </si>
   <si>
-    <t>客户型号</t>
+    <t>客户型号-单个客户唯一</t>
+  </si>
+  <si>
+    <t>产品特性</t>
   </si>
   <si>
     <t>数量</t>
@@ -325,7 +328,7 @@
     </r>
   </si>
   <si>
-    <t>WEPETBTRAN</t>
+    <t>颜色，客户下单OE,自行备注</t>
   </si>
   <si>
     <r>
@@ -483,6 +486,9 @@
   </si>
   <si>
     <t>PM10304</t>
+  </si>
+  <si>
+    <t>导入</t>
   </si>
   <si>
     <t>基础毛利率可修改</t>
@@ -1879,7 +1885,9 @@
   <cols>
     <col min="1" max="4" width="18.325" style="1" customWidth="1"/>
     <col min="5" max="5" width="24.8333333333333" style="1" customWidth="1"/>
-    <col min="6" max="9" width="18.325" style="1" customWidth="1"/>
+    <col min="6" max="7" width="18.325" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.2" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.325" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.10833333333333" style="1" customWidth="1"/>
     <col min="11" max="12" width="18.325" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.225" style="1" customWidth="1"/>
@@ -1904,7 +1912,7 @@
     <col min="16384" max="16384" width="18.325" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:41">
+    <row r="1" ht="27" spans="1:41">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1930,103 +1938,103 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AL1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AN1" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AO1" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" ht="139" customHeight="1" spans="1:41">
@@ -2034,24 +2042,24 @@
         <v>45926</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="12" t="s">
         <v>45</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="J2" s="14">
         <v>50</v>
@@ -2063,15 +2071,15 @@
         <v>875</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2" s="17"/>
       <c r="O2" s="17"/>
       <c r="P2" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R2" s="20">
         <v>95</v>
@@ -2083,54 +2091,54 @@
         <v>20</v>
       </c>
       <c r="U2" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V2" s="21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W2" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X2" s="21">
         <v>20260101</v>
       </c>
       <c r="Y2" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
       <c r="AB2" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AC2" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AE2" s="11"/>
       <c r="AF2" s="11"/>
       <c r="AG2" s="24"/>
       <c r="AH2" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AI2" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
       <c r="AM2" s="11"/>
       <c r="AN2" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO2" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="50" customHeight="1" spans="1:41">
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1">
         <v>12612289</v>
@@ -2138,7 +2146,9 @@
       <c r="E3" s="27"/>
       <c r="F3" s="27"/>
       <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+      <c r="H3" s="27" t="s">
+        <v>62</v>
+      </c>
       <c r="I3" s="27"/>
       <c r="J3" s="27"/>
       <c r="K3" s="27"/>
@@ -2147,7 +2157,7 @@
       <c r="N3" s="27"/>
       <c r="O3" s="27"/>
       <c r="P3" s="28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q3" s="28"/>
       <c r="R3" s="28"/>
@@ -2174,7 +2184,7 @@
       <c r="N4" s="27"/>
       <c r="O4" s="27"/>
       <c r="P4" s="28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="28"/>
       <c r="R4" s="28"/>
@@ -2263,32 +2273,37 @@
       <c r="Z7" s="28"/>
       <c r="AA7" s="28"/>
     </row>
+    <row r="8" spans="1:41">
+      <c r="D8" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="9" ht="80" customHeight="1" spans="1:41">
       <c r="N9" s="29" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O9" s="29"/>
       <c r="P9" s="29"/>
       <c r="Q9" s="29"/>
       <c r="R9" s="29"/>
       <c r="V9" s="30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="W9" s="30"/>
       <c r="AB9" s="30" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AC9" s="30"/>
       <c r="AO9" s="31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:41">
       <c r="P10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
